--- a/EXCEL/class notes/day3 count if/countifs Pivot.xlsx
+++ b/EXCEL/class notes/day3 count if/countifs Pivot.xlsx
@@ -1,38 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Advance excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day3 count if\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A9B07B-2D21-4FFC-92DD-1D2E0579A3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD70B1E9-7982-4A1F-A9B6-A636077D071F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{5DC9685A-84A7-4603-BBE7-00BB233B36FC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{5DC9685A-84A7-4603-BBE7-00BB233B36FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId6"/>
+    <pivotCache cacheId="5" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -227,6 +236,12 @@
   </si>
   <si>
     <t>Veritical value 3 time F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =COUNTIFS(E:E,"English",C:C,"&gt;34")</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -333,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -366,35 +381,43 @@
     <xf numFmtId="15" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -406,13 +429,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -458,111 +474,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -577,7 +488,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Admin" refreshedDate="45754.859488194445" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{908BB5E0-6DEE-4C21-97B6-EA5FBEF0C591}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Prashant" refreshedDate="45924.635659259256" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{908BB5E0-6DEE-4C21-97B6-EA5FBEF0C591}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:E31" sheet="Sheet3"/>
   </cacheSource>
@@ -598,10 +509,13 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-04-05T00:00:00" maxDate="2025-04-08T00:00:00" count="3">
-        <d v="2025-04-07T00:00:00"/>
-        <d v="2025-04-06T00:00:00"/>
-        <d v="2025-04-05T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-04-05T00:00:00" maxDate="2025-09-25T00:00:00" count="6">
+        <d v="2025-09-24T00:00:00"/>
+        <d v="2025-09-23T00:00:00"/>
+        <d v="2025-09-22T00:00:00"/>
+        <d v="2025-04-07T00:00:00" u="1"/>
+        <d v="2025-04-06T00:00:00" u="1"/>
+        <d v="2025-04-05T00:00:00" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -829,8 +743,93 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B795ADE-3C96-4E8A-9EE0-1F8810912875}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
-  <location ref="A3:D8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D677789-B20F-459B-B96C-FEF7D1204491}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
+  <location ref="G7:K11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" numFmtId="14" showAll="0">
+      <items count="7">
+        <item m="1" x="5"/>
+        <item m="1" x="4"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name=" " fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="4">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="3" count="0"/>
+          <reference field="4" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE5D3F22-0E87-4EF5-84AE-43B26D8FF713}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
+  <location ref="M8:P13" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -843,10 +842,13 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="4">
+      <items count="7">
+        <item m="1" x="5"/>
+        <item m="1" x="4"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item x="1"/>
         <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -856,13 +858,13 @@
   </rowFields>
   <rowItems count="4">
     <i>
-      <x/>
+      <x v="3"/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="4"/>
     </i>
     <i>
-      <x v="2"/>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -886,92 +888,7 @@
     <dataField name="Count of Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE5D3F22-0E87-4EF5-84AE-43B26D8FF713}" name="PivotTable3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
-  <location ref="M8:P13" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="3"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="4">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="0"/>
@@ -996,32 +913,52 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D677789-B20F-459B-B96C-FEF7D1204491}" name="PivotTable2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
-  <location ref="G7:K11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B795ADE-3C96-4E8A-9EE0-1F8810912875}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
+  <location ref="A3:D8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisCol" showAll="0">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisCol" numFmtId="14" showAll="0">
-      <items count="4">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="7">
+        <item m="1" x="5"/>
+        <item m="1" x="4"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item x="1"/>
         <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
   <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
     <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
+  </colFields>
+  <colItems count="3">
     <i>
       <x/>
     </i>
@@ -1031,38 +968,31 @@
     <i t="grand">
       <x/>
     </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
   </colItems>
   <dataFields count="1">
     <dataField name="Count of Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="21">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
+  <formats count="3">
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
           <reference field="3" count="0"/>
-          <reference field="4" count="0" selected="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -1375,12 +1305,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0A78157-2177-4204-9D44-74678824E53D}">
   <dimension ref="A1:P31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1397,7 +1327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1001</v>
       </c>
@@ -1425,7 +1355,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -1453,7 +1383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1003</v>
       </c>
@@ -1485,7 +1415,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1004</v>
       </c>
@@ -1513,7 +1443,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1005</v>
       </c>
@@ -1538,7 +1468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1006</v>
       </c>
@@ -1556,7 +1486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>1007</v>
       </c>
@@ -1584,7 +1514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1008</v>
       </c>
@@ -1608,6 +1538,9 @@
         <f>COUNTIFS(E:E,"English",C:C,"&gt;34")</f>
         <v>7</v>
       </c>
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
       <c r="L9" t="s">
         <v>24</v>
       </c>
@@ -1619,7 +1552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1009</v>
       </c>
@@ -1655,7 +1588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>1010</v>
       </c>
@@ -1688,7 +1621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>1001</v>
       </c>
@@ -1717,7 +1650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>1002</v>
       </c>
@@ -1746,7 +1679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>1003</v>
       </c>
@@ -1764,7 +1697,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>1004</v>
       </c>
@@ -1786,7 +1719,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>1005</v>
       </c>
@@ -1803,8 +1736,12 @@
       <c r="E16" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H16">
+        <f>COUNTIFS(E:E,"English",C:C,"&gt;34")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>1006</v>
       </c>
@@ -1822,7 +1759,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>1007</v>
       </c>
@@ -1840,7 +1777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>1008</v>
       </c>
@@ -1858,7 +1795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>1009</v>
       </c>
@@ -1876,7 +1813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>1010</v>
       </c>
@@ -1894,7 +1831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>1001</v>
       </c>
@@ -1912,7 +1849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>1002</v>
       </c>
@@ -1930,7 +1867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>1003</v>
       </c>
@@ -1948,7 +1885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>1004</v>
       </c>
@@ -1966,7 +1903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>1005</v>
       </c>
@@ -1984,7 +1921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>1006</v>
       </c>
@@ -2002,7 +1939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>1007</v>
       </c>
@@ -2020,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>1008</v>
       </c>
@@ -2038,7 +1975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>1009</v>
       </c>
@@ -2056,7 +1993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>1010</v>
       </c>
@@ -2084,14 +2021,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41926815-1767-4295-8CBC-70061598184D}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2108,7 +2045,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1001</v>
       </c>
@@ -2117,7 +2054,7 @@
       </c>
       <c r="C2" s="7">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D2" s="8" t="str">
         <f ca="1">IF(C2&gt;34,"Pass","Fail")</f>
@@ -2125,13 +2062,13 @@
       </c>
       <c r="E2" s="13">
         <f ca="1">TODAY()</f>
-        <v>45754</v>
+        <v>45924</v>
       </c>
       <c r="G2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>1002</v>
       </c>
@@ -2140,7 +2077,7 @@
       </c>
       <c r="C3" s="7">
         <f t="shared" ref="C3:C31" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="8" t="str">
         <f t="shared" ref="D3:D31" ca="1" si="1">IF(C3&gt;34,"Pass","Fail")</f>
@@ -2148,10 +2085,10 @@
       </c>
       <c r="E3" s="13">
         <f t="shared" ref="E3:E11" ca="1" si="2">TODAY()</f>
-        <v>45754</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>1003</v>
       </c>
@@ -2160,7 +2097,7 @@
       </c>
       <c r="C4" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="D4" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2168,17 +2105,17 @@
       </c>
       <c r="E4" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45754</v>
+        <v>45924</v>
       </c>
       <c r="G4" s="14">
         <f ca="1">TODAY()</f>
-        <v>45754</v>
+        <v>45924</v>
       </c>
       <c r="J4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1004</v>
       </c>
@@ -2187,21 +2124,21 @@
       </c>
       <c r="C5" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="D5" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="E5" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45754</v>
+        <v>45924</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>1005</v>
       </c>
@@ -2210,18 +2147,18 @@
       </c>
       <c r="C6" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="D6" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="E6" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45754</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>1006</v>
       </c>
@@ -2230,7 +2167,7 @@
       </c>
       <c r="C7" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D7" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2238,13 +2175,13 @@
       </c>
       <c r="E7" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45754</v>
+        <v>45924</v>
       </c>
       <c r="G7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>1007</v>
       </c>
@@ -2253,18 +2190,18 @@
       </c>
       <c r="C8" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D8" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="E8" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45754</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>1008</v>
       </c>
@@ -2273,7 +2210,7 @@
       </c>
       <c r="C9" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D9" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2281,7 +2218,7 @@
       </c>
       <c r="E9" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45754</v>
+        <v>45924</v>
       </c>
       <c r="G9" s="15">
         <v>45754</v>
@@ -2290,7 +2227,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>1009</v>
       </c>
@@ -2299,7 +2236,7 @@
       </c>
       <c r="C10" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D10" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2307,7 +2244,7 @@
       </c>
       <c r="E10" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45754</v>
+        <v>45924</v>
       </c>
       <c r="G10" t="s">
         <v>43</v>
@@ -2316,7 +2253,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>1010</v>
       </c>
@@ -2325,7 +2262,7 @@
       </c>
       <c r="C11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D11" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2333,10 +2270,10 @@
       </c>
       <c r="E11" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45754</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>1001</v>
       </c>
@@ -2345,7 +2282,7 @@
       </c>
       <c r="C12" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="D12" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2353,10 +2290,10 @@
       </c>
       <c r="E12" s="16">
         <f ca="1">E2-1</f>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>1002</v>
       </c>
@@ -2365,7 +2302,7 @@
       </c>
       <c r="C13" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D13" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2373,10 +2310,10 @@
       </c>
       <c r="E13" s="16">
         <f t="shared" ref="E13:E31" ca="1" si="3">E3-1</f>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>1003</v>
       </c>
@@ -2385,18 +2322,18 @@
       </c>
       <c r="C14" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D14" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="E14" s="16">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>1004</v>
       </c>
@@ -2405,18 +2342,21 @@
       </c>
       <c r="C15" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D15" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="E15" s="16">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+      <c r="G15" s="29">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>1005</v>
       </c>
@@ -2425,18 +2365,19 @@
       </c>
       <c r="C16" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D16" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="E16" s="16">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+      <c r="H16" s="29"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>1006</v>
       </c>
@@ -2445,7 +2386,7 @@
       </c>
       <c r="C17" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D17" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2453,10 +2394,10 @@
       </c>
       <c r="E17" s="16">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>1007</v>
       </c>
@@ -2465,7 +2406,7 @@
       </c>
       <c r="C18" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="D18" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2473,10 +2414,10 @@
       </c>
       <c r="E18" s="16">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>1008</v>
       </c>
@@ -2485,18 +2426,18 @@
       </c>
       <c r="C19" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="D19" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="E19" s="16">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>1009</v>
       </c>
@@ -2505,18 +2446,18 @@
       </c>
       <c r="C20" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D20" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="E20" s="16">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>1010</v>
       </c>
@@ -2525,7 +2466,7 @@
       </c>
       <c r="C21" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D21" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2533,10 +2474,10 @@
       </c>
       <c r="E21" s="16">
         <f t="shared" ca="1" si="3"/>
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>1001</v>
       </c>
@@ -2545,7 +2486,7 @@
       </c>
       <c r="C22" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D22" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2553,10 +2494,10 @@
       </c>
       <c r="E22" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>1002</v>
       </c>
@@ -2565,18 +2506,18 @@
       </c>
       <c r="C23" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="D23" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="E23" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>1003</v>
       </c>
@@ -2585,18 +2526,18 @@
       </c>
       <c r="C24" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="D24" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="E24" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>1004</v>
       </c>
@@ -2605,18 +2546,18 @@
       </c>
       <c r="C25" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="D25" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="E25" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>1005</v>
       </c>
@@ -2625,18 +2566,18 @@
       </c>
       <c r="C26" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D26" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="E26" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>1006</v>
       </c>
@@ -2645,18 +2586,18 @@
       </c>
       <c r="C27" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="D27" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="E27" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>1007</v>
       </c>
@@ -2665,7 +2606,7 @@
       </c>
       <c r="C28" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D28" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2673,10 +2614,10 @@
       </c>
       <c r="E28" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>1008</v>
       </c>
@@ -2685,7 +2626,7 @@
       </c>
       <c r="C29" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D29" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2693,10 +2634,10 @@
       </c>
       <c r="E29" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>1009</v>
       </c>
@@ -2705,18 +2646,18 @@
       </c>
       <c r="C30" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D30" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="E30" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>1010</v>
       </c>
@@ -2725,7 +2666,7 @@
       </c>
       <c r="C31" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="D31" s="8" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2733,7 +2674,7 @@
       </c>
       <c r="E31" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>45752</v>
+        <v>45922</v>
       </c>
     </row>
   </sheetData>
@@ -2743,989 +2684,986 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBDF522-11BE-43BF-875A-E847220EEF1E}">
-  <dimension ref="A3:D8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0339A8C1-638D-41AD-8C53-179C389E0002}">
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="7">
+        <v>87</v>
+      </c>
+      <c r="D2" s="8" t="str">
+        <f>IF(C2&gt;34,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="E2" s="13">
+        <f ca="1">TODAY()</f>
+        <v>45924</v>
+      </c>
+      <c r="H2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="7">
+        <v>100</v>
+      </c>
+      <c r="D3" s="8" t="str">
+        <f t="shared" ref="D3:D31" si="0">IF(C3&gt;34,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="E3" s="13">
+        <f t="shared" ref="E3:E11" ca="1" si="1">TODAY()</f>
+        <v>45924</v>
+      </c>
+      <c r="H3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="7">
+        <v>69</v>
+      </c>
+      <c r="D4" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E4" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45924</v>
+      </c>
+      <c r="M4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="7">
+        <v>51</v>
+      </c>
+      <c r="D5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E5" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45924</v>
+      </c>
+      <c r="M5" t="s">
+        <v>62</v>
+      </c>
+      <c r="N5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="7">
+        <v>64</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E6" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="7">
+        <v>17</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="E7" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45924</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46</v>
+      </c>
+      <c r="D8" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E8" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45924</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="14">
+        <v>45924</v>
+      </c>
+      <c r="I8" s="14">
+        <v>45923</v>
+      </c>
+      <c r="J8" s="14">
+        <v>45922</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="N8" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="7">
+        <v>80</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E9" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45924</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="31">
+        <v>2</v>
+      </c>
+      <c r="I9" s="31">
+        <v>3</v>
+      </c>
+      <c r="J9" s="31">
+        <v>1</v>
+      </c>
+      <c r="K9" s="30">
+        <v>6</v>
+      </c>
+      <c r="M9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="N9" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="O9" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="P9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="23">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="7">
+        <v>15</v>
+      </c>
+      <c r="D10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="E10" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45924</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="31">
+        <v>8</v>
+      </c>
+      <c r="I10" s="31">
+        <v>7</v>
+      </c>
+      <c r="J10" s="31">
+        <v>9</v>
+      </c>
+      <c r="K10" s="30">
+        <v>24</v>
+      </c>
+      <c r="M10" s="20">
+        <v>45924</v>
+      </c>
+      <c r="N10" s="31">
+        <v>2</v>
+      </c>
+      <c r="O10" s="31">
+        <v>8</v>
+      </c>
+      <c r="P10" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="7">
+        <v>64</v>
+      </c>
+      <c r="D11" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E11" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45924</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="30">
+        <v>10</v>
+      </c>
+      <c r="I11" s="30">
+        <v>10</v>
+      </c>
+      <c r="J11" s="30">
+        <v>10</v>
+      </c>
+      <c r="K11" s="30">
+        <v>30</v>
+      </c>
+      <c r="M11" s="20">
+        <v>45923</v>
+      </c>
+      <c r="N11" s="31">
+        <v>3</v>
+      </c>
+      <c r="O11" s="31">
+        <v>7</v>
+      </c>
+      <c r="P11" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>1001</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="7">
+        <v>32</v>
+      </c>
+      <c r="D12" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="E12" s="16">
+        <f ca="1">E2-1</f>
+        <v>45923</v>
+      </c>
+      <c r="M12" s="20">
+        <v>45922</v>
+      </c>
+      <c r="N12" s="31">
+        <v>1</v>
+      </c>
+      <c r="O12" s="31">
+        <v>9</v>
+      </c>
+      <c r="P12" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>1002</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="7">
+        <v>41</v>
+      </c>
+      <c r="D13" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E13" s="16">
+        <f t="shared" ref="E13:E31" ca="1" si="2">E3-1</f>
+        <v>45923</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13" s="30">
+        <v>6</v>
+      </c>
+      <c r="O13" s="30">
+        <v>24</v>
+      </c>
+      <c r="P13" s="30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>1003</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="7">
+        <v>66</v>
+      </c>
+      <c r="D14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E14" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45923</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="27">
+        <f ca="1">I14-1</f>
+        <v>45922</v>
+      </c>
+      <c r="I14" s="27">
+        <f ca="1">J14-1</f>
+        <v>45923</v>
+      </c>
+      <c r="J14" s="27">
+        <f ca="1">TODAY()</f>
+        <v>45924</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
+        <v>1004</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="7">
+        <v>48</v>
+      </c>
+      <c r="D15" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E15" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45923</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="1">
+        <f ca="1">COUNTIFS($D:$D,$G15,$E:$E,H$14)</f>
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" ref="I15:J16" ca="1" si="3">COUNTIFS($D:$D,$G15,$E:$E,I$14)</f>
+        <v>3</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <f>COUNTIFS($D:$D,$G15)</f>
+        <v>6</v>
+      </c>
+      <c r="L15">
+        <f>COUNTIFS($D:$D,$G15)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>1005</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="7">
+        <v>76</v>
+      </c>
+      <c r="D16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45923</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="1">
+        <f ca="1">COUNTIFS($D:$D,$G16,$E:$E,H$14)</f>
+        <v>9</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" ca="1" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="K16">
+        <f>COUNTIFS($D:$D,$G16)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
+        <v>1006</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="7">
+        <v>95</v>
+      </c>
+      <c r="D17" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E17" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45923</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="25">
+        <f ca="1">COUNTIFS($E:$E,H$14)</f>
+        <v>10</v>
+      </c>
+      <c r="I17" s="25">
+        <f ca="1">COUNTIFS($E:$E,I$14)</f>
+        <v>10</v>
+      </c>
+      <c r="J17" s="25">
+        <f ca="1">COUNTIFS($E:$E,J$14)</f>
+        <v>10</v>
+      </c>
+      <c r="K17" s="25">
+        <f>COUNTA(A:A)-1</f>
+        <v>30</v>
+      </c>
+      <c r="M17" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="P17" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>1007</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="7">
+        <v>92</v>
+      </c>
+      <c r="D18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E18" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45923</v>
+      </c>
+      <c r="H18" s="25">
+        <f ca="1">COUNTIFS($E:$E,H$14)</f>
+        <v>10</v>
+      </c>
+      <c r="K18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="20">
         <v>45752</v>
       </c>
-      <c r="B5" s="18">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18">
-        <v>9</v>
-      </c>
-      <c r="D5" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="23">
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
+        <v>1008</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="7">
+        <v>15</v>
+      </c>
+      <c r="D19" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="E19" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45923</v>
+      </c>
+      <c r="M19" s="20">
         <v>45753</v>
       </c>
-      <c r="B6" s="18">
-        <v>3</v>
-      </c>
-      <c r="C6" s="18">
-        <v>7</v>
-      </c>
-      <c r="D6" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="23">
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
+        <v>1009</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="7">
+        <v>100</v>
+      </c>
+      <c r="D20" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E20" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45923</v>
+      </c>
+      <c r="M20" s="20">
         <v>45754</v>
       </c>
-      <c r="B7" s="18">
-        <v>2</v>
-      </c>
-      <c r="C7" s="18">
-        <v>8</v>
-      </c>
-      <c r="D7" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="21" t="s">
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
+        <v>1010</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="7">
+        <v>19</v>
+      </c>
+      <c r="D21" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="E21" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45923</v>
+      </c>
+      <c r="M21" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="18">
-        <v>6</v>
-      </c>
-      <c r="C8" s="18">
-        <v>24</v>
-      </c>
-      <c r="D8" s="18">
-        <v>30</v>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="7">
+        <v>84</v>
+      </c>
+      <c r="D22" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E22" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="7">
+        <v>65</v>
+      </c>
+      <c r="D23" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E23" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="7">
+        <v>53</v>
+      </c>
+      <c r="D24" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E24" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="7">
+        <v>83</v>
+      </c>
+      <c r="D25" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E25" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="7">
+        <v>36</v>
+      </c>
+      <c r="D26" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E26" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="7">
+        <v>76</v>
+      </c>
+      <c r="D27" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E27" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="7">
+        <v>87</v>
+      </c>
+      <c r="D28" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E28" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="7">
+        <v>86</v>
+      </c>
+      <c r="D29" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E29" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="7">
+        <v>14</v>
+      </c>
+      <c r="D30" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="E30" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="7">
+        <v>53</v>
+      </c>
+      <c r="D31" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="E31" s="17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45922</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0339A8C1-638D-41AD-8C53-179C389E0002}">
-  <dimension ref="A1:P31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBDF522-11BE-43BF-875A-E847220EEF1E}">
+  <dimension ref="A3:D8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="32">
+        <v>45924</v>
+      </c>
+      <c r="B5" s="30">
+        <v>2</v>
+      </c>
+      <c r="C5" s="30">
+        <v>8</v>
+      </c>
+      <c r="D5" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="32">
+        <v>45923</v>
+      </c>
+      <c r="B6" s="30">
+        <v>3</v>
+      </c>
+      <c r="C6" s="30">
+        <v>7</v>
+      </c>
+      <c r="D6" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="32">
+        <v>45922</v>
+      </c>
+      <c r="B7" s="30">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="C7" s="30">
+        <v>9</v>
+      </c>
+      <c r="D7" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="30">
+        <v>6</v>
+      </c>
+      <c r="C8" s="30">
+        <v>24</v>
+      </c>
+      <c r="D8" s="30">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="7">
-        <v>87</v>
-      </c>
-      <c r="D2" s="8" t="str">
-        <f>IF(C2&gt;34,"Pass","Fail")</f>
-        <v>Pass</v>
-      </c>
-      <c r="E2" s="13">
-        <f ca="1">TODAY()</f>
-        <v>45754</v>
-      </c>
-      <c r="H2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="12">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="7">
-        <v>100</v>
-      </c>
-      <c r="D3" s="8" t="str">
-        <f t="shared" ref="D3:D31" si="0">IF(C3&gt;34,"Pass","Fail")</f>
-        <v>Pass</v>
-      </c>
-      <c r="E3" s="13">
-        <f t="shared" ref="E3:E11" ca="1" si="1">TODAY()</f>
-        <v>45754</v>
-      </c>
-      <c r="H3" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="7">
-        <v>69</v>
-      </c>
-      <c r="D4" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E4" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>45754</v>
-      </c>
-      <c r="M4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="12">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="7">
-        <v>51</v>
-      </c>
-      <c r="D5" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E5" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>45754</v>
-      </c>
-      <c r="M5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="7">
-        <v>64</v>
-      </c>
-      <c r="D6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E6" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>45754</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="12">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="7">
-        <v>17</v>
-      </c>
-      <c r="D7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Fail</v>
-      </c>
-      <c r="E7" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>45754</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="7">
-        <v>46</v>
-      </c>
-      <c r="D8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E8" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>45754</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="14">
-        <v>45752</v>
-      </c>
-      <c r="I8" s="14">
-        <v>45753</v>
-      </c>
-      <c r="J8" s="14">
-        <v>45754</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="12">
-        <v>1008</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="7">
-        <v>80</v>
-      </c>
-      <c r="D9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E9" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>45754</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="25">
-        <v>1</v>
-      </c>
-      <c r="I9" s="25">
-        <v>3</v>
-      </c>
-      <c r="J9" s="25">
-        <v>2</v>
-      </c>
-      <c r="K9" s="18">
-        <v>6</v>
-      </c>
-      <c r="M9" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="12">
-        <v>1009</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="7">
-        <v>15</v>
-      </c>
-      <c r="D10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Fail</v>
-      </c>
-      <c r="E10" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>45754</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="25">
-        <v>9</v>
-      </c>
-      <c r="I10" s="25">
-        <v>7</v>
-      </c>
-      <c r="J10" s="25">
-        <v>8</v>
-      </c>
-      <c r="K10" s="18">
-        <v>24</v>
-      </c>
-      <c r="M10" s="21">
-        <v>45752</v>
-      </c>
-      <c r="N10" s="25">
-        <v>1</v>
-      </c>
-      <c r="O10" s="25">
-        <v>9</v>
-      </c>
-      <c r="P10" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
-        <v>1010</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="7">
-        <v>64</v>
-      </c>
-      <c r="D11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E11" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>45754</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="18">
-        <v>10</v>
-      </c>
-      <c r="I11" s="18">
-        <v>10</v>
-      </c>
-      <c r="J11" s="18">
-        <v>10</v>
-      </c>
-      <c r="K11" s="18">
-        <v>30</v>
-      </c>
-      <c r="M11" s="21">
-        <v>45753</v>
-      </c>
-      <c r="N11" s="25">
-        <v>3</v>
-      </c>
-      <c r="O11" s="25">
-        <v>7</v>
-      </c>
-      <c r="P11" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="9">
-        <v>1001</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="7">
-        <v>32</v>
-      </c>
-      <c r="D12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Fail</v>
-      </c>
-      <c r="E12" s="16">
-        <f ca="1">E2-1</f>
-        <v>45753</v>
-      </c>
-      <c r="M12" s="21">
-        <v>45754</v>
-      </c>
-      <c r="N12" s="25">
-        <v>2</v>
-      </c>
-      <c r="O12" s="25">
-        <v>8</v>
-      </c>
-      <c r="P12" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="9">
-        <v>1002</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="7">
-        <v>41</v>
-      </c>
-      <c r="D13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E13" s="16">
-        <f t="shared" ref="E13:E31" ca="1" si="2">E3-1</f>
-        <v>45753</v>
-      </c>
-      <c r="M13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="N13" s="18">
-        <v>6</v>
-      </c>
-      <c r="O13" s="18">
-        <v>24</v>
-      </c>
-      <c r="P13" s="18">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="9">
-        <v>1003</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="7">
-        <v>66</v>
-      </c>
-      <c r="D14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E14" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="G14" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="30">
-        <f ca="1">I14-1</f>
-        <v>45752</v>
-      </c>
-      <c r="I14" s="30">
-        <f ca="1">J14-1</f>
-        <v>45753</v>
-      </c>
-      <c r="J14" s="30">
-        <f ca="1">TODAY()</f>
-        <v>45754</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="9">
-        <v>1004</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="7">
-        <v>48</v>
-      </c>
-      <c r="D15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E15" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="25">
-        <f ca="1">COUNTIFS($D:$D,$G15,$E:$E,H$14)</f>
-        <v>1</v>
-      </c>
-      <c r="I15" s="25">
-        <f t="shared" ref="I15:J16" ca="1" si="3">COUNTIFS($D:$D,$G15,$E:$E,I$14)</f>
-        <v>3</v>
-      </c>
-      <c r="J15" s="25">
-        <f t="shared" ca="1" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="K15" s="18">
-        <f>COUNTIFS($D:$D,$G15)</f>
-        <v>6</v>
-      </c>
-      <c r="L15" s="18">
-        <f>COUNTIFS($D:$D,$G15)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="9">
-        <v>1005</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="7">
-        <v>76</v>
-      </c>
-      <c r="D16" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E16" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="25">
-        <f ca="1">COUNTIFS($D:$D,$G16,$E:$E,H$14)</f>
-        <v>9</v>
-      </c>
-      <c r="I16" s="25">
-        <f t="shared" ca="1" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="J16" s="25">
-        <f t="shared" ca="1" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="K16" s="18">
-        <f>COUNTIFS($D:$D,$G16)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A17" s="9">
-        <v>1006</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="7">
-        <v>95</v>
-      </c>
-      <c r="D17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E17" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="28">
-        <f ca="1">COUNTIFS($E:$E,H$14)</f>
-        <v>10</v>
-      </c>
-      <c r="I17" s="28">
-        <f ca="1">COUNTIFS($E:$E,I$14)</f>
-        <v>10</v>
-      </c>
-      <c r="J17" s="28">
-        <f ca="1">COUNTIFS($E:$E,J$14)</f>
-        <v>10</v>
-      </c>
-      <c r="K17" s="28">
-        <f>COUNTA(A:A)-1</f>
-        <v>30</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="N17" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="O17" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="P17" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="9">
-        <v>1007</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="7">
-        <v>92</v>
-      </c>
-      <c r="D18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E18" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="H18" s="28">
-        <f ca="1">COUNTIFS($E:$E,H$14)</f>
-        <v>10</v>
-      </c>
-      <c r="K18" t="s">
-        <v>52</v>
-      </c>
-      <c r="M18" s="21">
-        <v>45752</v>
-      </c>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="18"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A19" s="9">
-        <v>1008</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="7">
-        <v>15</v>
-      </c>
-      <c r="D19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Fail</v>
-      </c>
-      <c r="E19" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="M19" s="21">
-        <v>45753</v>
-      </c>
-      <c r="N19" s="25"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="18"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A20" s="9">
-        <v>1009</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="7">
-        <v>100</v>
-      </c>
-      <c r="D20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E20" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="M20" s="21">
-        <v>45754</v>
-      </c>
-      <c r="N20" s="25"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="18"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="9">
-        <v>1010</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="7">
-        <v>19</v>
-      </c>
-      <c r="D21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Fail</v>
-      </c>
-      <c r="E21" s="16">
-        <f t="shared" ca="1" si="2"/>
-        <v>45753</v>
-      </c>
-      <c r="M21" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="28"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
-        <v>1001</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="7">
-        <v>84</v>
-      </c>
-      <c r="D22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E22" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="6">
-        <v>1002</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="7">
-        <v>65</v>
-      </c>
-      <c r="D23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E23" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="6">
-        <v>1003</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="7">
-        <v>53</v>
-      </c>
-      <c r="D24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E24" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A25" s="6">
-        <v>1004</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="7">
-        <v>83</v>
-      </c>
-      <c r="D25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E25" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A26" s="6">
-        <v>1005</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="7">
-        <v>36</v>
-      </c>
-      <c r="D26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E26" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A27" s="6">
-        <v>1006</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="7">
-        <v>76</v>
-      </c>
-      <c r="D27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E27" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A28" s="6">
-        <v>1007</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="7">
-        <v>87</v>
-      </c>
-      <c r="D28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E28" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" s="6">
-        <v>1008</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="7">
-        <v>86</v>
-      </c>
-      <c r="D29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E29" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A30" s="6">
-        <v>1009</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="7">
-        <v>14</v>
-      </c>
-      <c r="D30" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Fail</v>
-      </c>
-      <c r="E30" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A31" s="6">
-        <v>1010</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="7">
-        <v>53</v>
-      </c>
-      <c r="D31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Pass</v>
-      </c>
-      <c r="E31" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>45752</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3733,9 +3671,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D90D2BE-A744-4613-95B2-F932E9A3D542}">
   <dimension ref="A1:S23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>55</v>
       </c>
@@ -3743,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1001</v>
       </c>
@@ -3760,7 +3698,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>1002</v>
       </c>
@@ -3774,7 +3712,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>1003</v>
       </c>
@@ -3782,7 +3720,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1004</v>
       </c>
@@ -3790,7 +3728,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>1005</v>
       </c>
@@ -3798,7 +3736,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>1006</v>
       </c>
@@ -3858,7 +3796,7 @@
         <v>Emp ID</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>1007</v>
       </c>
@@ -3898,7 +3836,7 @@
         <v>Name</v>
       </c>
       <c r="O8">
-        <f t="shared" ref="O8:S8" si="5">$A2</f>
+        <f t="shared" ref="O8:T8" si="5">$A2</f>
         <v>1001</v>
       </c>
       <c r="P8">
@@ -3918,7 +3856,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>1008</v>
       </c>
@@ -3958,7 +3896,7 @@
         <v>Name</v>
       </c>
       <c r="O9">
-        <f t="shared" ref="O9:S9" si="7">$A3</f>
+        <f t="shared" ref="O9:T9" si="7">$A3</f>
         <v>1002</v>
       </c>
       <c r="P9">
@@ -3978,7 +3916,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>1009</v>
       </c>
@@ -4018,7 +3956,7 @@
         <v>Name</v>
       </c>
       <c r="O10">
-        <f t="shared" ref="O10:S10" si="9">$A4</f>
+        <f t="shared" ref="O10:T10" si="9">$A4</f>
         <v>1003</v>
       </c>
       <c r="P10">
@@ -4038,7 +3976,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>1010</v>
       </c>
@@ -4078,7 +4016,7 @@
         <v>Name</v>
       </c>
       <c r="O11">
-        <f t="shared" ref="O11:S11" si="11">$A5</f>
+        <f t="shared" ref="O11:T11" si="11">$A5</f>
         <v>1004</v>
       </c>
       <c r="P11">
@@ -4098,7 +4036,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D12" s="4">
         <f t="shared" ref="D12:E12" si="12">A6</f>
         <v>1005</v>
@@ -4132,7 +4070,7 @@
         <v>Name</v>
       </c>
       <c r="O12">
-        <f t="shared" ref="O12:S12" si="13">$A6</f>
+        <f t="shared" ref="O12:T12" si="13">$A6</f>
         <v>1005</v>
       </c>
       <c r="P12">
@@ -4152,7 +4090,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D13" s="4">
         <f t="shared" ref="D13:E13" si="14">A7</f>
         <v>1006</v>
@@ -4186,7 +4124,7 @@
         <v>Name</v>
       </c>
       <c r="O13">
-        <f t="shared" ref="O13:S13" si="15">$A7</f>
+        <f t="shared" ref="O13:T13" si="15">$A7</f>
         <v>1006</v>
       </c>
       <c r="P13">
@@ -4206,7 +4144,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D14" s="4">
         <f t="shared" ref="D14:E14" si="16">A8</f>
         <v>1007</v>
@@ -4240,7 +4178,7 @@
         <v>Name</v>
       </c>
       <c r="O14">
-        <f t="shared" ref="O14:S14" si="17">$A8</f>
+        <f t="shared" ref="O14:T14" si="17">$A8</f>
         <v>1007</v>
       </c>
       <c r="P14">
@@ -4260,7 +4198,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D15" s="4">
         <f t="shared" ref="D15:E15" si="18">A9</f>
         <v>1008</v>
@@ -4294,7 +4232,7 @@
         <v>Name</v>
       </c>
       <c r="O15">
-        <f t="shared" ref="O15:S15" si="19">$A9</f>
+        <f t="shared" ref="O15:T15" si="19">$A9</f>
         <v>1008</v>
       </c>
       <c r="P15">
@@ -4314,7 +4252,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D16" s="4">
         <f t="shared" ref="D16:E16" si="20">A10</f>
         <v>1009</v>
@@ -4348,7 +4286,7 @@
         <v>Name</v>
       </c>
       <c r="O16">
-        <f t="shared" ref="O16:S16" si="21">$A10</f>
+        <f t="shared" ref="O16:T16" si="21">$A10</f>
         <v>1009</v>
       </c>
       <c r="P16">
@@ -4368,7 +4306,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17" spans="4:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D17" s="4">
         <f t="shared" ref="D17:E17" si="22">A11</f>
         <v>1010</v>
@@ -4402,7 +4340,7 @@
         <v>Name</v>
       </c>
       <c r="O17">
-        <f t="shared" ref="O17:S17" si="23">$A11</f>
+        <f t="shared" ref="O17:T17" si="23">$A11</f>
         <v>1010</v>
       </c>
       <c r="P17">
@@ -4422,7 +4360,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="18" spans="4:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D18" s="4">
         <f t="shared" ref="D18:E18" si="24">A12</f>
         <v>0</v>
@@ -4476,7 +4414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="4:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D19" s="4">
         <f t="shared" ref="D19:E19" si="26">A13</f>
         <v>0</v>
@@ -4530,7 +4468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="4:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:19" x14ac:dyDescent="0.3">
       <c r="G20" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Emp ID</v>
@@ -4556,7 +4494,7 @@
         <v>Name</v>
       </c>
     </row>
-    <row r="21" spans="4:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="4:19" x14ac:dyDescent="0.3">
       <c r="G21" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Emp ID</v>
@@ -4582,7 +4520,7 @@
         <v>Name</v>
       </c>
     </row>
-    <row r="22" spans="4:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="4:19" x14ac:dyDescent="0.3">
       <c r="G22" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Emp ID</v>
@@ -4600,7 +4538,7 @@
         <v>Emp ID</v>
       </c>
     </row>
-    <row r="23" spans="4:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="4:19" x14ac:dyDescent="0.3">
       <c r="G23" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Emp ID</v>
